--- a/tests/fixtures/expenses/max_minimal.xlsx
+++ b/tests/fixtures/expenses/max_minimal.xlsx
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2097.83</v>
+        <v>-268.43</v>
       </c>
       <c r="D7" t="n">
-        <v>-2097.83</v>
+        <v>-268.43</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
